--- a/Team-Data/2007-08/1-30-2007-08.xlsx
+++ b/Team-Data/2007-08/1-30-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.442</v>
+        <v>0.452</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L2" t="n">
         <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O2" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P2" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R2" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S2" t="n">
         <v>29.9</v>
       </c>
       <c r="T2" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U2" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V2" t="n">
         <v>15.4</v>
@@ -730,25 +797,25 @@
         <v>21.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
@@ -757,7 +824,7 @@
         <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>23</v>
@@ -781,16 +848,16 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
         <v>21</v>
@@ -802,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>11.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -948,10 +1015,10 @@
         <v>9</v>
       </c>
       <c r="AM3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
@@ -969,7 +1036,7 @@
         <v>8</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -978,10 +1045,10 @@
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -1025,52 +1092,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
         <v>6.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N4" t="n">
         <v>0.361</v>
       </c>
       <c r="O4" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.704</v>
+        <v>0.707</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T4" t="n">
         <v>40.2</v>
@@ -1079,16 +1146,16 @@
         <v>21.7</v>
       </c>
       <c r="V4" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X4" t="n">
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z4" t="n">
         <v>22.6</v>
@@ -1097,19 +1164,19 @@
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>22</v>
@@ -1118,13 +1185,13 @@
         <v>5</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1142,13 +1209,13 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1157,13 +1224,13 @@
         <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX4" t="n">
         <v>14</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="H5" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>35.5</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="K5" t="n">
-        <v>0.419</v>
+        <v>0.421</v>
       </c>
       <c r="L5" t="n">
         <v>5.4</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="O5" t="n">
         <v>17.5</v>
@@ -1249,49 +1316,49 @@
         <v>0.749</v>
       </c>
       <c r="R5" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="T5" t="n">
         <v>43.8</v>
       </c>
       <c r="U5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z5" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>21</v>
-      </c>
       <c r="AA5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
@@ -1300,7 +1367,7 @@
         <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1315,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>23</v>
@@ -1330,19 +1397,19 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>15</v>
@@ -1351,7 +1418,7 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>16</v>
@@ -1360,7 +1427,7 @@
         <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -1389,58 +1456,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
         <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.8</v>
       </c>
       <c r="I6" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J6" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
         <v>6.4</v>
       </c>
       <c r="M6" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.352</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
         <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="R6" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S6" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U6" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V6" t="n">
         <v>14.6</v>
@@ -1452,28 +1519,28 @@
         <v>4.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA6" t="n">
         <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1482,19 +1549,19 @@
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
       </c>
       <c r="AM6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN6" t="n">
         <v>17</v>
@@ -1512,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG7" t="n">
         <v>5</v>
@@ -1667,7 +1734,7 @@
         <v>11</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
         <v>5</v>
@@ -1676,10 +1743,10 @@
         <v>18</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1691,16 +1758,16 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -1753,31 +1820,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.591</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J8" t="n">
         <v>85</v>
       </c>
       <c r="K8" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L8" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
         <v>18.3</v>
@@ -1786,43 +1853,43 @@
         <v>0.331</v>
       </c>
       <c r="O8" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="P8" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S8" t="n">
         <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="AB8" t="n">
         <v>106.1</v>
@@ -1831,7 +1898,7 @@
         <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1852,13 +1919,13 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>17</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
         <v>26</v>
@@ -1879,19 +1946,19 @@
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY8" t="n">
         <v>18</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -2013,28 +2080,28 @@
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
@@ -2058,7 +2125,7 @@
         <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
         <v>22</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="n">
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>0.596</v>
+        <v>0.587</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="J10" t="n">
         <v>88.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
         <v>9.800000000000001</v>
@@ -2147,34 +2214,34 @@
         <v>27.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O10" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P10" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="R10" t="n">
         <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U10" t="n">
         <v>22.9</v>
       </c>
       <c r="V10" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="X10" t="n">
         <v>4.4</v>
@@ -2183,31 +2250,31 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>109.3</v>
+        <v>109.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2228,10 +2295,10 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP10" t="n">
         <v>12</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>13</v>
       </c>
       <c r="AQ10" t="n">
         <v>19</v>
@@ -2243,16 +2310,16 @@
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="n">
         <v>20</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -2377,22 +2444,22 @@
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
         <v>12</v>
@@ -2410,7 +2477,7 @@
         <v>24</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2434,13 +2501,13 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
         <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
         <v>6</v>
@@ -2452,7 +2519,7 @@
         <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12" t="n">
         <v>20</v>
@@ -2589,10 +2656,10 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -2616,10 +2683,10 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.333</v>
+        <v>0.317</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J13" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="N13" t="n">
         <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P13" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R13" t="n">
         <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T13" t="n">
         <v>41.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V13" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W13" t="n">
         <v>6.7</v>
@@ -2729,7 +2796,7 @@
         <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA13" t="n">
         <v>21.8</v>
@@ -2738,19 +2805,19 @@
         <v>94.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.4</v>
+        <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
         <v>30</v>
       </c>
       <c r="AE13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
         <v>17</v>
@@ -2762,13 +2829,13 @@
         <v>20</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
@@ -2780,13 +2847,13 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
         <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
         <v>20</v>
@@ -2801,22 +2868,22 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>12</v>
       </c>
       <c r="BB13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC13" t="n">
         <v>24</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>23</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2959,7 +3026,7 @@
         <v>2</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>17</v>
@@ -2971,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.283</v>
+        <v>0.289</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>80.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M15" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.37</v>
+        <v>0.374</v>
       </c>
       <c r="O15" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="T15" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U15" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
         <v>16</v>
@@ -3090,25 +3157,25 @@
         <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
         <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC15" t="n">
         <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI15" t="n">
         <v>9</v>
@@ -3135,10 +3202,10 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>18</v>
@@ -3147,16 +3214,16 @@
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>28</v>
@@ -3180,7 +3247,7 @@
         <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3230,16 +3297,16 @@
         <v>77.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
         <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O16" t="n">
         <v>18.2</v>
@@ -3248,34 +3315,34 @@
         <v>25.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="R16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S16" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="U16" t="n">
         <v>19.7</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X16" t="n">
         <v>4.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
         <v>22</v>
@@ -3284,16 +3351,16 @@
         <v>93.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG16" t="n">
         <v>29</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3317,16 +3384,16 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>18</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3341,16 +3408,16 @@
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
         <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>0.383</v>
+        <v>0.391</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
-        <v>80.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>5.6</v>
@@ -3421,31 +3488,31 @@
         <v>16.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P17" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="R17" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T17" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V17" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W17" t="n">
         <v>6.9</v>
@@ -3454,19 +3521,19 @@
         <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA17" t="n">
         <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.2</v>
+        <v>94.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.8</v>
+        <v>-6</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,19 +3542,19 @@
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK17" t="n">
         <v>18</v>
@@ -3496,13 +3563,13 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP17" t="n">
         <v>25</v>
@@ -3511,7 +3578,7 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3520,31 +3587,31 @@
         <v>26</v>
       </c>
       <c r="AU17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
         <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J18" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L18" t="n">
         <v>5.5</v>
@@ -3603,25 +3670,25 @@
         <v>16.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.723</v>
+        <v>0.722</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U18" t="n">
         <v>18.9</v>
@@ -3630,7 +3697,7 @@
         <v>15.5</v>
       </c>
       <c r="W18" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
         <v>3.9</v>
@@ -3639,28 +3706,28 @@
         <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8</v>
+        <v>-8.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH18" t="n">
         <v>29</v>
@@ -3669,10 +3736,10 @@
         <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3681,7 +3748,7 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>29</v>
@@ -3690,28 +3757,28 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
         <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3723,10 +3790,10 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>-5.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3857,7 +3924,7 @@
         <v>29</v>
       </c>
       <c r="AL19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM19" t="n">
         <v>17</v>
@@ -3875,7 +3942,7 @@
         <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
@@ -3884,10 +3951,10 @@
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3902,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.711</v>
+        <v>0.727</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,7 +4022,7 @@
         <v>38.2</v>
       </c>
       <c r="J20" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K20" t="n">
         <v>0.458</v>
@@ -3967,7 +4034,7 @@
         <v>20.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O20" t="n">
         <v>15.3</v>
@@ -3976,25 +4043,25 @@
         <v>19.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>31.3</v>
       </c>
       <c r="T20" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U20" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>4</v>
@@ -4003,19 +4070,19 @@
         <v>4.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA20" t="n">
         <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -4024,7 +4091,7 @@
         <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="n">
         <v>12</v>
@@ -4036,28 +4103,28 @@
         <v>7</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
         <v>13</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -4119,34 +4186,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>0.311</v>
+        <v>0.318</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J21" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M21" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N21" t="n">
         <v>0.336</v>
@@ -4164,16 +4231,16 @@
         <v>12.5</v>
       </c>
       <c r="S21" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U21" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W21" t="n">
         <v>6.4</v>
@@ -4185,19 +4252,19 @@
         <v>5.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA21" t="n">
         <v>21.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4206,7 +4273,7 @@
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
         <v>20</v>
@@ -4218,7 +4285,7 @@
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>20</v>
@@ -4242,19 +4309,19 @@
         <v>4</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4272,7 +4339,7 @@
         <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -4301,64 +4368,64 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" t="n">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.617</v>
+        <v>0.609</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J22" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="K22" t="n">
         <v>0.465</v>
       </c>
       <c r="L22" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="N22" t="n">
         <v>0.363</v>
       </c>
       <c r="O22" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.5</v>
+        <v>29.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.722</v>
       </c>
       <c r="R22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W22" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="X22" t="n">
         <v>4.6</v>
@@ -4373,10 +4440,10 @@
         <v>24.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4397,7 +4464,7 @@
         <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4409,16 +4476,16 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
         <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
         <v>27</v>
@@ -4427,25 +4494,25 @@
         <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY22" t="n">
         <v>6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -4483,61 +4550,61 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
         <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.391</v>
+        <v>0.378</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J23" t="n">
         <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
         <v>11.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.316</v>
+        <v>0.319</v>
       </c>
       <c r="O23" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="R23" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="S23" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T23" t="n">
         <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="W23" t="n">
         <v>8.199999999999999</v>
@@ -4549,40 +4616,40 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH23" t="n">
         <v>22</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>22</v>
       </c>
-      <c r="AH23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4609,19 +4676,19 @@
         <v>29</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
         <v>17</v>
@@ -4633,10 +4700,10 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>6.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
         <v>28</v>
@@ -4791,22 +4858,22 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW24" t="n">
         <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -4847,61 +4914,61 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" t="n">
         <v>26</v>
       </c>
       <c r="F25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.578</v>
+        <v>0.591</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J25" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M25" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.392</v>
+        <v>0.395</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R25" t="n">
         <v>10.4</v>
       </c>
       <c r="S25" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T25" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U25" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V25" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W25" t="n">
         <v>5.6</v>
@@ -4916,37 +4983,37 @@
         <v>20.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.2</v>
+        <v>96.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG25" t="n">
         <v>10</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>2</v>
       </c>
       <c r="AI25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>11</v>
@@ -4970,13 +5037,13 @@
         <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
         <v>28</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
@@ -4985,19 +5052,19 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.455</v>
+        <v>0.442</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="K26" t="n">
         <v>0.46</v>
@@ -5056,10 +5123,10 @@
         <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O26" t="n">
         <v>21.8</v>
@@ -5068,67 +5135,67 @@
         <v>27.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.794</v>
+        <v>0.796</v>
       </c>
       <c r="R26" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S26" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T26" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="U26" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="V26" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA26" t="n">
         <v>23.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>15</v>
@@ -5137,22 +5204,22 @@
         <v>18</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP26" t="n">
         <v>8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5167,7 +5234,7 @@
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AY26" t="n">
         <v>21</v>
@@ -5182,7 +5249,7 @@
         <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF27" t="n">
         <v>7</v>
@@ -5304,10 +5371,10 @@
         <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK27" t="n">
         <v>12</v>
@@ -5331,7 +5398,7 @@
         <v>15</v>
       </c>
       <c r="AR27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS27" t="n">
         <v>14</v>
@@ -5340,7 +5407,7 @@
         <v>21</v>
       </c>
       <c r="AU27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5349,7 +5416,7 @@
         <v>24</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>13</v>
@@ -5358,10 +5425,10 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC27" t="n">
         <v>8</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5483,10 +5550,10 @@
         <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>3</v>
@@ -5495,10 +5562,10 @@
         <v>28</v>
       </c>
       <c r="AL28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN28" t="n">
         <v>27</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5534,7 +5601,7 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -5575,37 +5642,37 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.556</v>
+        <v>0.545</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J29" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="M29" t="n">
         <v>18.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.423</v>
+        <v>0.416</v>
       </c>
       <c r="O29" t="n">
         <v>16.2</v>
@@ -5614,70 +5681,70 @@
         <v>20</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
         <v>30.7</v>
       </c>
       <c r="T29" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V29" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH29" t="n">
         <v>6</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5695,13 +5762,13 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
         <v>25</v>
@@ -5719,7 +5786,7 @@
         <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5787,58 +5854,58 @@
         <v>11.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.356</v>
+        <v>0.361</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="P30" t="n">
-        <v>28.8</v>
+        <v>29</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T30" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U30" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="V30" t="n">
         <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AA30" t="n">
         <v>23.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.2</v>
+        <v>105.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5865,10 +5932,10 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
@@ -5939,106 +6006,106 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" t="n">
         <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
-        <v>0.545</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="K31" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L31" t="n">
         <v>6.7</v>
       </c>
       <c r="M31" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N31" t="n">
         <v>0.347</v>
       </c>
       <c r="O31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P31" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="R31" t="n">
         <v>12.2</v>
       </c>
       <c r="S31" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T31" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U31" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA31" t="n">
         <v>19.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
         <v>12</v>
@@ -6050,13 +6117,13 @@
         <v>18</v>
       </c>
       <c r="AO31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -6065,16 +6132,16 @@
         <v>16</v>
       </c>
       <c r="AT31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
@@ -6086,13 +6153,13 @@
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-30-2007-08</t>
+          <t>2008-01-30</t>
         </is>
       </c>
     </row>
